--- a/artfynd/A 32222-2026 artfynd.xlsx
+++ b/artfynd/A 32222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136133205</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136133182</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136133387</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136133617</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136132502</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136133374</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2026 artfynd.xlsx
+++ b/artfynd/A 32222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136133205</v>
       </c>
       <c r="B2" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136133182</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136133387</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136133617</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2026 artfynd.xlsx
+++ b/artfynd/A 32222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136133205</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136133182</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136133387</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136133617</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136132412</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136132602</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136132979</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136133087</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136133138</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136132502</v>
       </c>
       <c r="B11" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136133374</v>
       </c>
       <c r="B12" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
